--- a/data/trans_orig/P62A$jubilacion-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144708</t>
+          <t>144278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160259</t>
+          <t>160183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72279</t>
+          <t>72378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198836</t>
+          <t>198782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230052</t>
+          <t>228727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190800</t>
+          <t>189956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208293</t>
+          <t>207753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55806</t>
+          <t>55240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222517</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260789</t>
+          <t>261818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79243</t>
+          <t>78804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103118</t>
+          <t>103344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77067</t>
+          <t>75517</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110630</t>
+          <t>109720</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122762</t>
+          <t>123173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140442</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160450</t>
+          <t>160751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192944</t>
+          <t>192817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49485</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>47548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73388</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>161544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178455</t>
+          <t>178158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62000</t>
+          <t>63419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>90344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229440</t>
+          <t>227777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>264376</t>
+          <t>265660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69761</t>
+          <t>67820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95617</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97530</t>
+          <t>98441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>638560</t>
+          <t>638499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>673151</t>
+          <t>672924</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202158</t>
+          <t>201156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248046</t>
+          <t>247086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>846704</t>
+          <t>847160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>915506</t>
+          <t>914828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>259080</t>
+          <t>262575</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>309304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>257740</t>
+          <t>256818</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>317638</t>
+          <t>314441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56950</t>
+          <t>57073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90081</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101582</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142040</t>
+          <t>140889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46446</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150393</t>
+          <t>150208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176241</t>
+          <t>175926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57549</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82161</t>
+          <t>84160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215978</t>
+          <t>214573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253551</t>
+          <t>253529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57521</t>
+          <t>59460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83276</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59125</t>
+          <t>58361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90449</t>
+          <t>89525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46296</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>33724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>61082</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44151</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165245</t>
+          <t>164043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193088</t>
+          <t>193608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90650</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232695</t>
+          <t>232586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278343</t>
+          <t>278421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71596</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101381</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>68872</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105634</t>
+          <t>104820</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>31939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33716</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51988</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>82220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34605</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68021</t>
+          <t>68532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110446</t>
+          <t>109273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135567</t>
+          <t>134637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53334</t>
+          <t>52932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145095</t>
+          <t>144656</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182608</t>
+          <t>182883</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56610</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83068</t>
+          <t>84386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>56224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>87585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>29775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>69423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31466</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>45969</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183391</t>
+          <t>183159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209433</t>
+          <t>209736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65651</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95124</t>
+          <t>95516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253112</t>
+          <t>255259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298223</t>
+          <t>298299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81710</t>
+          <t>79573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111300</t>
+          <t>111369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80486</t>
+          <t>79652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115004</t>
+          <t>114167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46776</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>36263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77481</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38813</t>
+          <t>40878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>56739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>637330</t>
+          <t>637078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>689653</t>
+          <t>692109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237356</t>
+          <t>239895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293882</t>
+          <t>295315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>890632</t>
+          <t>887821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>970909</t>
+          <t>971263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>297014</t>
+          <t>292984</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>352025</t>
+          <t>349248</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>294999</t>
+          <t>295256</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>360593</t>
+          <t>361475</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121069</t>
+          <t>119227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167919</t>
+          <t>166327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97897</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192494</t>
+          <t>194534</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252181</t>
+          <t>252031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77561</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78344</t>
+          <t>77718</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115435</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>132079</t>
+          <t>131474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>182666</t>
+          <t>183044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>152724</t>
+          <t>152121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172485</t>
+          <t>173022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56943</t>
+          <t>57819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83494</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214155</t>
+          <t>214846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250072</t>
+          <t>250525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>63594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39306</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>65471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22111</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200191</t>
+          <t>199228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225506</t>
+          <t>225333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79026</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>110125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>286182</t>
+          <t>286482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329042</t>
+          <t>327776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55950</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84526</t>
+          <t>84951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>88011</t>
+          <t>87891</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>60521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41173</t>
+          <t>41233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62328</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143498</t>
+          <t>143283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164309</t>
+          <t>164729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45197</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70242</t>
+          <t>70412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>196093</t>
+          <t>194718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>231460</t>
+          <t>231157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42590</t>
+          <t>41641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66595</t>
+          <t>66887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>70250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>39051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>36485</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205378</t>
+          <t>205818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231069</t>
+          <t>231741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80363</t>
+          <t>79261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114273</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293237</t>
+          <t>293769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339518</t>
+          <t>339737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72630</t>
+          <t>74044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107059</t>
+          <t>106576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72221</t>
+          <t>72895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108213</t>
+          <t>111126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57076</t>
+          <t>55471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62928</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>53862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>84910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>728215</t>
+          <t>726361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>776258</t>
+          <t>774060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290214</t>
+          <t>288316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347978</t>
+          <t>346981</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1032356</t>
+          <t>1028731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1109783</t>
+          <t>1105522</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>235428</t>
+          <t>235152</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>293005</t>
+          <t>292433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>234046</t>
+          <t>236126</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>295889</t>
+          <t>298549</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>71692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109097</t>
+          <t>106875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>40367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68248</t>
+          <t>72055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119920</t>
+          <t>119274</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168861</t>
+          <t>166609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74670</t>
+          <t>75868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89612</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128867</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>145433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>196679</t>
+          <t>195121</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87589</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110240</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57444</t>
+          <t>56869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134082</t>
+          <t>134244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>162310</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42200</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>68830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85750</t>
+          <t>85769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>71821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92750</t>
+          <t>92494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -8608,12 +8608,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81997</t>
+          <t>82135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93278</t>
+          <t>92261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116661</t>
+          <t>116803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>60986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142650</t>
+          <t>142837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173386</t>
+          <t>172698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>40559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71245</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90547</t>
+          <t>91434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>70428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94154</t>
+          <t>94090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51927</t>
+          <t>51430</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74000</t>
+          <t>74794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>83703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111284</t>
+          <t>112992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>91069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117907</t>
+          <t>117101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95744</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324343</t>
+          <t>317918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218900</t>
+          <t>221437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>465652</t>
+          <t>467555</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83365</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126220</t>
+          <t>127507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93623</t>
+          <t>91065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>165040</t>
+          <t>164933</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9605,12 +9605,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97416</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122226</t>
+          <t>123326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77710</t>
+          <t>78605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99721</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183291</t>
+          <t>183825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215909</t>
+          <t>217939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42294</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57866</t>
+          <t>58358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>69888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90543</t>
+          <t>90837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70370</t>
+          <t>69296</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94520</t>
+          <t>94726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64571</t>
+          <t>65278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88686</t>
+          <t>88463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113953</t>
+          <t>114835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145290</t>
+          <t>145004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>394198</t>
+          <t>395485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>442602</t>
+          <t>444252</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286820</t>
+          <t>286160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>680323</t>
+          <t>674187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>726665</t>
+          <t>725456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1146732</t>
+          <t>1152980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>112018</t>
+          <t>111262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150339</t>
+          <t>149374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125638</t>
+          <t>122995</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>225476</t>
+          <t>224531</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142082</t>
+          <t>150140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>377571</t>
+          <t>379394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198735</t>
+          <t>198670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348746</t>
+          <t>349740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10432,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>218331</t>
+          <t>217117</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265915</t>
+          <t>264657</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>78212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201462</t>
+          <t>203284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255724</t>
+          <t>255174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>455137</t>
+          <t>457237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62A$jubilacion-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144278</t>
+          <t>142848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160183</t>
+          <t>160211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50621</t>
+          <t>50785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72378</t>
+          <t>71979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198782</t>
+          <t>198687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228727</t>
+          <t>229420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>40968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>62947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>40384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>65775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,49 +974,49 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10451</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18420</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>14,54%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5708</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18021</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>27</t>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>37028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189956</t>
+          <t>188683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207753</t>
+          <t>207815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55240</t>
+          <t>54467</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223928</t>
+          <t>222785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261818</t>
+          <t>260571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78804</t>
+          <t>78892</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103344</t>
+          <t>102625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>75653</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123173</t>
+          <t>123748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>140956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>34947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55356</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160751</t>
+          <t>160234</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192817</t>
+          <t>192133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49432</t>
+          <t>48963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>70267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47548</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74294</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161544</t>
+          <t>161619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178158</t>
+          <t>179069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63419</t>
+          <t>63127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90344</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227777</t>
+          <t>229548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265660</t>
+          <t>264303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67820</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>95250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66649</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98441</t>
+          <t>99138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40910</t>
+          <t>41106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>638499</t>
+          <t>639437</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>672924</t>
+          <t>672786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201156</t>
+          <t>202254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>249874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>847160</t>
+          <t>850179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>914828</t>
+          <t>919693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>261261</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>309755</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>255092</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>314441</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>99271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140889</t>
+          <t>142305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>46759</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150208</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175926</t>
+          <t>176184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>55910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84160</t>
+          <t>82144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214573</t>
+          <t>215696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253529</t>
+          <t>253542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59460</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84647</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58361</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89525</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>43815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40809</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164043</t>
+          <t>164973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193608</t>
+          <t>194078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60276</t>
+          <t>62035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232586</t>
+          <t>233309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278421</t>
+          <t>275165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>72210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100488</t>
+          <t>102999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104820</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>56319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51375</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82220</t>
+          <t>82535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>44070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68532</t>
+          <t>67537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109273</t>
+          <t>110084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134637</t>
+          <t>134877</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29592</t>
+          <t>29618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52932</t>
+          <t>52112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144656</t>
+          <t>144271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182883</t>
+          <t>183990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84386</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56224</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87585</t>
+          <t>87122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39572</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69423</t>
+          <t>67236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45969</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183159</t>
+          <t>182888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209736</t>
+          <t>210608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64982</t>
+          <t>65145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255259</t>
+          <t>255527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298299</t>
+          <t>298024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79573</t>
+          <t>81421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111369</t>
+          <t>112033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79652</t>
+          <t>80298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56739</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>637078</t>
+          <t>637702</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>692109</t>
+          <t>690614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239895</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295315</t>
+          <t>294932</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>887821</t>
+          <t>888787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>971263</t>
+          <t>971285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>292984</t>
+          <t>297201</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>349248</t>
+          <t>351962</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>295256</t>
+          <t>293362</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>361475</t>
+          <t>360159</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119227</t>
+          <t>121248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166327</t>
+          <t>166025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,82 +5310,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>78409</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>62373</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>98199</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>221358</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>193943</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>253555</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>78409</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>61610</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>97220</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>221358</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>194534</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>252031</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76997</t>
+          <t>77035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77718</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>119181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>131474</t>
+          <t>131836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>183044</t>
+          <t>181554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>152121</t>
+          <t>152707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173022</t>
+          <t>172314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81857</t>
+          <t>82600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214846</t>
+          <t>215757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250525</t>
+          <t>249586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63594</t>
+          <t>64295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39285</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65471</t>
+          <t>65233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40695</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199228</t>
+          <t>199572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225333</t>
+          <t>225766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79711</t>
+          <t>80053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>109440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>286482</t>
+          <t>287000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327776</t>
+          <t>330584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53883</t>
+          <t>53797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84951</t>
+          <t>82558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>55692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87891</t>
+          <t>88949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44590</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41233</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143283</t>
+          <t>143455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164729</t>
+          <t>164544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>45717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70412</t>
+          <t>70805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194718</t>
+          <t>194831</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>231157</t>
+          <t>230902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41641</t>
+          <t>42637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66887</t>
+          <t>67384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41286</t>
+          <t>41168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70250</t>
+          <t>70304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>37990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>36383</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205818</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231741</t>
+          <t>230910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79261</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113456</t>
+          <t>115259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293769</t>
+          <t>292014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339737</t>
+          <t>339528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>72279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106576</t>
+          <t>106359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111126</t>
+          <t>111230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>57127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>63091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53862</t>
+          <t>52337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84910</t>
+          <t>82880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>726361</t>
+          <t>730260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>774060</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288316</t>
+          <t>288692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346981</t>
+          <t>346949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1028731</t>
+          <t>1033720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1105522</t>
+          <t>1108884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>235152</t>
+          <t>236685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>292433</t>
+          <t>291509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236126</t>
+          <t>234246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>298549</t>
+          <t>297540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71692</t>
+          <t>71919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106875</t>
+          <t>107131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72055</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119274</t>
+          <t>118089</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>164143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75868</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>129165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>145433</t>
+          <t>144074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>195121</t>
+          <t>193592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98386</t>
+          <t>108013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87514</t>
+          <t>94838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>119985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56869</t>
+          <t>61598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>147614</t>
+          <t>160974</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134244</t>
+          <t>146025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163041</t>
+          <t>175866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>64726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77421</t>
+          <t>81496</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>91639</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>81791</t>
+          <t>85942</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71821</t>
+          <t>74314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92494</t>
+          <t>98953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -8603,32 +8603,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>57868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8638,32 +8638,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37743</t>
+          <t>40340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8673,32 +8673,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>68828</t>
+          <t>77035</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57666</t>
+          <t>64229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82135</t>
+          <t>92219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>105408</t>
+          <t>116269</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92261</t>
+          <t>102784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116803</t>
+          <t>129306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>58586</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>50145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60986</t>
+          <t>68954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>157521</t>
+          <t>174856</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142837</t>
+          <t>159084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172698</t>
+          <t>191522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40559</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>88633</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>78498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>98672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>88633</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>75712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94090</t>
+          <t>101927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -9059,32 +9059,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>69863</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51430</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74794</t>
+          <t>83307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9094,32 +9094,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>50065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9129,32 +9129,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97850</t>
+          <t>110548</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83703</t>
+          <t>95546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>125105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103551</t>
+          <t>119295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>104952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117101</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>246067</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93494</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>317918</t>
+          <t>57841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>349618</t>
+          <t>167799</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221437</t>
+          <t>148838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>467555</t>
+          <t>185574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51841</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>50870</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80510</t>
+          <t>64234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>55167</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127507</t>
+          <t>65214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>59597</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>48029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91065</t>
+          <t>72419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -9515,32 +9515,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>72472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>59388</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77287</t>
+          <t>86344</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9550,32 +9550,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88724</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9585,32 +9585,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>98050</t>
+          <t>110532</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38077</t>
+          <t>94028</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>164933</t>
+          <t>127143</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111034</t>
+          <t>114121</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>101336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123326</t>
+          <t>127922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78605</t>
+          <t>85143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>110637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>199710</t>
+          <t>211690</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183825</t>
+          <t>193329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217939</t>
+          <t>227573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42118</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>21711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>46093</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>60787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -9858,17 +9858,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69888</t>
+          <t>74159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90837</t>
+          <t>97326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>82386</t>
+          <t>88675</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>76786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>103597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -9971,32 +9971,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76448</t>
+          <t>82381</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65278</t>
+          <t>70446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88463</t>
+          <t>96383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10006,32 +10006,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53350</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>48011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>68407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10041,32 +10041,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>140480</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114835</t>
+          <t>125079</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145004</t>
+          <t>156940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>457699</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>395485</t>
+          <t>430253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>444252</t>
+          <t>485431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286160</t>
+          <t>238666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>674187</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>854463</t>
+          <t>715317</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>725456</t>
+          <t>683385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1152980</t>
+          <t>748748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111262</t>
+          <t>116805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149374</t>
+          <t>157654</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>55192</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122995</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>224531</t>
+          <t>227978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150140</t>
+          <t>291430</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>379394</t>
+          <t>332244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>299495</t>
+          <t>322848</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198670</t>
+          <t>299363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>349740</t>
+          <t>350622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -10427,32 +10427,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217117</t>
+          <t>244560</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264657</t>
+          <t>294498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10462,32 +10462,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78212</t>
+          <t>150263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203284</t>
+          <t>186524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10497,32 +10497,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>438594</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255174</t>
+          <t>408488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457237</t>
+          <t>471254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
